--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486809_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486809_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.3616</v>
+        <v>11.3067</v>
       </c>
       <c r="E2" t="n">
-        <v>8.666499999999999</v>
+        <v>7.7357</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6951</v>
+        <v>3.5709</v>
       </c>
       <c r="G2" t="n">
         <v>7.8829</v>
@@ -610,13 +610,13 @@
         <v>3.0892</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5793</v>
+        <v>-0.4757</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8268</v>
+        <v>-0.104</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2475</v>
+        <v>-0.3716</v>
       </c>
       <c r="V2" t="n">
         <v>2.741</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9826</v>
+        <v>2.141</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6006</v>
+        <v>1.3797</v>
       </c>
       <c r="F3" t="n">
-        <v>1.382</v>
+        <v>0.7612</v>
       </c>
       <c r="G3" t="n">
         <v>1.0995</v>
@@ -688,13 +688,13 @@
         <v>2.8962</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0477</v>
+        <v>-0.8894</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2968</v>
+        <v>-0.5177</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2492</v>
+        <v>-0.3716</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7587</v>
+        <v>1.0166</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7484</v>
+        <v>1.907</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9897</v>
+        <v>-0.8903</v>
       </c>
       <c r="G4" t="n">
         <v>1.7271</v>
@@ -766,13 +766,13 @@
         <v>0.7723</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.513</v>
+        <v>-0.2551</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4415</v>
+        <v>-0.2829</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0716</v>
+        <v>0.0278</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2277</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5165</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="E5" t="n">
         <v>0.4409</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0755</v>
+        <v>0.1997</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4905</v>
@@ -844,13 +844,13 @@
         <v>0.1931</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4137</v>
+        <v>-0.2896</v>
       </c>
       <c r="T5" t="n">
         <v>-0.2207</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.193</v>
+        <v>-0.0689</v>
       </c>
       <c r="V5" t="n">
         <v>1.2277</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3617</v>
+        <v>-0.0514</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3814</v>
+        <v>-0.0711</v>
       </c>
       <c r="F6" t="n">
         <v>0.0196</v>
@@ -922,10 +922,10 @@
         <v>2.1239</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2135</v>
+        <v>-0.9033</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8554</v>
+        <v>-0.5451</v>
       </c>
       <c r="U6" t="n">
         <v>-0.3581</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7503</v>
+        <v>-0.9861</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.855</v>
+        <v>-1.1653</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1047</v>
+        <v>0.1792</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1033</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.353</v>
+        <v>0.1172</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5239</v>
+        <v>0.2137</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1709</v>
+        <v>-0.0965</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9295</v>
+        <v>-1.0315</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.658</v>
+        <v>-1.8097</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7285</v>
+        <v>0.7782</v>
       </c>
       <c r="G8" t="n">
         <v>1.3684</v>
@@ -1078,13 +1078,13 @@
         <v>2.1239</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2979</v>
+        <v>-0.3999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1107</v>
+        <v>-0.2624</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1871</v>
+        <v>-0.1375</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2277</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3888</v>
+        <v>-1.0578</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5992</v>
+        <v>-1.3923</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2103</v>
+        <v>0.3345</v>
       </c>
       <c r="G9" t="n">
         <v>0.1601</v>
@@ -1156,13 +1156,13 @@
         <v>0.9654</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6068</v>
+        <v>-0.2758</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.607</v>
+        <v>-0.4002</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0002</v>
+        <v>0.1243</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9421</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7502</v>
+        <v>-1.9557</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.6577</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6631</v>
+        <v>-2.6134</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0244</v>
@@ -1234,13 +1234,13 @@
         <v>1.3515</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1157</v>
+        <v>-0.0897</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0825</v>
+        <v>-0.1726</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0332</v>
+        <v>0.0829</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2277</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5272</v>
+        <v>-2.221</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2548</v>
+        <v>-3.048</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7276</v>
+        <v>0.827</v>
       </c>
       <c r="G11" t="n">
         <v>0.9372</v>
@@ -1312,13 +1312,13 @@
         <v>1.3515</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9544</v>
+        <v>-0.6482</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6622</v>
+        <v>-0.4553</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2922</v>
+        <v>-0.1928</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8451</v>
+        <v>-2.7747</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2483</v>
+        <v>-2.3517</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5968</v>
+        <v>-0.423</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5729</v>
@@ -1390,13 +1390,13 @@
         <v>1.9308</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7669</v>
+        <v>-0.6965</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0273</v>
+        <v>-0.0761</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7942</v>
+        <v>-0.6204</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4707</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.1591</v>
+        <v>-3.7399</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4879</v>
+        <v>-3.019</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6712</v>
+        <v>-0.7209</v>
       </c>
       <c r="G13" t="n">
         <v>-0.3635</v>
@@ -1468,13 +1468,13 @@
         <v>1.5446</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8881</v>
+        <v>-0.4689</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5795</v>
+        <v>-0.1106</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3087</v>
+        <v>-0.3583</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5559</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9074999999999998</v>
+        <v>1.286799999999997</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.115400000000001</v>
+        <v>-0.7360999999999995</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0225</v>
+        <v>2.022699999999999</v>
       </c>
       <c r="G14" t="n">
         <v>9.275300000000001</v>
@@ -1546,10 +1546,10 @@
         <v>18.3424</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.654</v>
+        <v>-5.2749</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.3133</v>
+        <v>-2.9339</v>
       </c>
       <c r="U14" t="n">
         <v>-2.3407</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0645</v>
+        <v>5.1446</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8967</v>
+        <v>3.6899</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1678</v>
+        <v>1.4547</v>
       </c>
       <c r="G15" t="n">
         <v>-0.3311</v>
@@ -1624,13 +1624,13 @@
         <v>3.0892</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1748</v>
+        <v>1.2549</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7439</v>
+        <v>0.5371</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4309</v>
+        <v>0.7178</v>
       </c>
       <c r="V15" t="n">
         <v>2.29</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4257</v>
+        <v>2.8478</v>
       </c>
       <c r="E16" t="n">
-        <v>2.455</v>
+        <v>1.9379</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9707</v>
+        <v>0.91</v>
       </c>
       <c r="G16" t="n">
         <v>0.7913</v>
@@ -1702,13 +1702,13 @@
         <v>2.51</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4949</v>
+        <v>0.917</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0199</v>
+        <v>0.5028</v>
       </c>
       <c r="U16" t="n">
-        <v>0.475</v>
+        <v>0.4143</v>
       </c>
       <c r="V16" t="n">
         <v>1.7188</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. NVE MALEVA</t>
+          <t>A. ROMERO GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9443</v>
+        <v>1.3162</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7231</v>
+        <v>1.2682</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2212</v>
+        <v>0.048</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.7439</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6686</v>
+        <v>0.6964</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1913</v>
+        <v>0.0475</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.311</v>
+        <v>1.0132</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3924</v>
+        <v>0.9725</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0814</v>
+        <v>0.0407</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8337</v>
+        <v>-0.2693</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2763</v>
+        <v>-0.2761</v>
       </c>
       <c r="O17" t="n">
-        <v>1.1099</v>
+        <v>0.0068</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3444</v>
+        <v>0.3792</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7372</v>
+        <v>0.255</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6072</v>
+        <v>0.1243</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0426</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ROMERO GARCIA</t>
+          <t>A. SOUSA SILVA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3451</v>
+        <v>1.1644</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3716</v>
+        <v>0.2325</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0265</v>
+        <v>0.9319</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7439</v>
+        <v>0.3548</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6964</v>
+        <v>0.477</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0475</v>
+        <v>-0.1222</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0132</v>
+        <v>2.9291</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9725</v>
+        <v>2.6849</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0407</v>
+        <v>0.2442</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2693</v>
+        <v>-2.5742</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2761</v>
+        <v>-2.2079</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0068</v>
+        <v>-0.3663</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-4.0546</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1931</v>
+        <v>2.8962</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4082</v>
+        <v>0.8205</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3584</v>
+        <v>0.1304</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0498</v>
+        <v>0.6901</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.1475</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.0801</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SOUSA SILVA</t>
+          <t>L. NVE MALEVA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3676</v>
+        <v>1.1307</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.112</v>
+        <v>-0.1042</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7444</v>
+        <v>1.2349</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3548</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.477</v>
+        <v>-0.6686</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1222</v>
+        <v>1.1913</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9291</v>
+        <v>-0.311</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6849</v>
+        <v>-0.3924</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2442</v>
+        <v>0.0814</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.5742</v>
+        <v>0.8337</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.2079</v>
+        <v>-0.2763</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3663</v>
+        <v>1.1099</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1585</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.0546</v>
+        <v>-1.9308</v>
       </c>
       <c r="R19" t="n">
-        <v>2.8962</v>
+        <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7116</v>
+        <v>1.5308</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2141</v>
+        <v>0.9099</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5026</v>
+        <v>0.6209</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1475</v>
+        <v>0.0426</v>
       </c>
       <c r="W19" t="n">
         <v>1.2277</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.0801</v>
+        <v>-1.1851</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2196</v>
+        <v>-2.5894</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.8283</v>
+        <v>-4.3112</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6087</v>
+        <v>1.7218</v>
       </c>
       <c r="G20" t="n">
         <v>-3.074</v>
@@ -2014,13 +2014,13 @@
         <v>1.5446</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5128</v>
+        <v>0.1173</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6898</v>
+        <v>-0.1727</v>
       </c>
       <c r="U20" t="n">
-        <v>0.177</v>
+        <v>0.2901</v>
       </c>
       <c r="V20" t="n">
         <v>1.7188</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.3125</v>
+        <v>-3.7995</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5607</v>
+        <v>-3.147</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7518</v>
+        <v>-0.6525</v>
       </c>
       <c r="G21" t="n">
         <v>-4.5618</v>
@@ -2092,13 +2092,13 @@
         <v>2.3169</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3419</v>
+        <v>0.8549</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2763</v>
+        <v>0.1374</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6182</v>
+        <v>0.7175</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2856</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7875</v>
+        <v>-5.4329</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-1.5887</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.8193</v>
+        <v>-3.8442</v>
       </c>
       <c r="G22" t="n">
         <v>-3.7211</v>
@@ -2170,13 +2170,13 @@
         <v>1.9308</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1143</v>
+        <v>0.4689</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6616</v>
+        <v>0.0411</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4527</v>
+        <v>0.4278</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0222</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9076000000000004</v>
+        <v>-0.2181000000000015</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0228</v>
+        <v>-2.022599999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1152</v>
+        <v>1.8046</v>
       </c>
       <c r="G23" t="n">
-        <v>-9.275299999999998</v>
+        <v>-9.2753</v>
       </c>
       <c r="H23" t="n">
         <v>-13.446</v>
@@ -2221,13 +2221,13 @@
         <v>4.1706</v>
       </c>
       <c r="J23" t="n">
-        <v>1.872600000000001</v>
+        <v>1.8726</v>
       </c>
       <c r="K23" t="n">
         <v>-2.061500000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>3.934099999999999</v>
+        <v>3.9341</v>
       </c>
       <c r="M23" t="n">
         <v>-11.1478</v>
@@ -2239,7 +2239,7 @@
         <v>0.2368000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.8961</v>
+        <v>-2.896100000000001</v>
       </c>
       <c r="Q23" t="n">
         <v>-18.3424</v>
@@ -2248,13 +2248,13 @@
         <v>15.4462</v>
       </c>
       <c r="S23" t="n">
-        <v>5.6541</v>
+        <v>6.3435</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3408</v>
+        <v>2.341</v>
       </c>
       <c r="U23" t="n">
-        <v>3.3134</v>
+        <v>4.002800000000001</v>
       </c>
       <c r="V23" t="n">
         <v>5.6099</v>
@@ -2263,7 +2263,7 @@
         <v>12.1065</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.4965</v>
+        <v>-6.496499999999999</v>
       </c>
     </row>
   </sheetData>
